--- a/LISTAS_ORDENADAS/MA/Fratachos Cinta de perciana Articulos de madera/CAJAS PARA ENRROLLADOR.xlsx
+++ b/LISTAS_ORDENADAS/MA/Fratachos Cinta de perciana Articulos de madera/CAJAS PARA ENRROLLADOR.xlsx
@@ -826,14 +826,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="n">
-        <v>45209.57788074074</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="15">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -855,8 +851,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="41.25" customHeight="1" s="15">
       <c r="A11" s="18" t="inlineStr">
         <is>
@@ -949,7 +943,6 @@
     <row r="32" ht="18" customHeight="1" s="15">
       <c r="E32" s="3" t="n"/>
     </row>
-    <row r="33"/>
     <row r="34" ht="15.75" customHeight="1" s="15">
       <c r="A34" s="4" t="n"/>
     </row>
@@ -958,12 +951,12 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
